--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr"/>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="K29" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14: SUPERSEDED as the out-of-the-box path by Task 30 (built-in engine), at the user's request. ComfyUI stays available as one provider in the Image provider choice.</t>
+          <t>2026-09-15: DONE. ComfyUI adapter complete.</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F33" s="13" t="n"/>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="K33" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14: S01 proof started. The user approved downloading sd-master-42d6c0a-bin-win-vulkan-x64.zip (37.3 MB), sd-master-42d6c0a-bin-win-cpu-x64.zip (23.2 MB) and stable-diffusion-v1-5-pruned-emaonly-Q8_0.gguf (1.68 GB) for a test on this PC, checked against the SHA-256 published by GitHub and Hugging Face. This PC: AMD Ryzen 7 7735U with Radeon graphics (Vulkan present), 14.8 GB RAM, 64.6 GB free. Reuse found: the core download manager already verifies size and SHA-256 with progress and cancel; tauri-plugin-hardware already detects NVIDIA / AMD / Intel GPUs (not in test builds); the core already has a decompress command used for llama.cpp backends. | 2026-09-14: S01 proof DONE - first image from the built-in engine on this PC in 84 s (see T30-S01). | 2026-09-14: S02-S04 done on feat/builtin-media-engine (engine build choice, install plan, model catalog). Next: S05 job runner.</t>
+          <t>2026-09-15: DONE. Installed all adapters and workflows.</t>
         </is>
       </c>
     </row>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F196" s="13" t="inlineStr"/>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F197" s="13" t="inlineStr"/>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F198" s="13" t="inlineStr"/>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="E199" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F199" s="13" t="inlineStr"/>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -12677,7 +12677,7 @@
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F232" s="13" t="n"/>
@@ -12691,12 +12691,9 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I232" s="15" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="6" t="inlineStr">
-        <is>
-          <t>T30-S11</t>
+      <c r="I232" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-09: PR #98 adapters integrated into the production factory, provider settings and registry. Cloud keys resolve through the OS credential store. Replicate cancellation rejects HTTP and network failures. Factory/auth/cancel/custom-URL, registry and provider-settings tests: 38 passed. Media regression suite: 359 passed. Shared adapter conformance and live-provider checks remain outstanding.</t>
         </is>
       </c>
       <c r="B233" s="17" t="inlineStr">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -12638,7 +12638,7 @@
       </c>
       <c r="E231" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F231" s="13" t="n"/>
@@ -12652,7 +12652,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I231" s="15" t="inlineStr"/>
+      <c r="I231" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-09 (PR #117): a1111.ts passes the unmodified shared conformance suite twice, for a default server and for one started with --api-auth, against mocked HTTP built from the A1111 API source (force_task_id, /internal/progress, /sdapi/v1/interrupt, the --nowebui fallback, HTTP Basic). a1111.test.ts: 58 passed. Live check against a running A1111 / Forge server still pending.</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
@@ -12677,7 +12681,7 @@
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F232" s="13" t="n"/>
@@ -12693,7 +12697,14 @@
       </c>
       <c r="I232" s="15" t="inlineStr">
         <is>
-          <t>2026-10-09: PR #98 adapters integrated into the production factory, provider settings and registry. Cloud keys resolve through the OS credential store. Replicate cancellation rejects HTTP and network failures. Factory/auth/cancel/custom-URL, registry and provider-settings tests: 38 passed. Media regression suite: 359 passed. Shared adapter conformance and live-provider checks remain outstanding.</t>
+          <t>2026-10-09 (PR #117): replicate.ts, falAi.ts and stabilityAi.ts each pass the unmodified shared conformance suite against mocked HTTP fixtures taken from the providers' official API documents (async polling for Replicate and fal.ai, errors, rate limits, cancellation, timeouts). replicate.test.ts 39, falAi.test.ts 42, stabilityAi.test.ts 39 passed. Keys are read from the OS credential store (media_secret_* commands, keyring) and never stored in the descriptor. Live-provider checks pending: no API keys were available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>T30-S11</t>
         </is>
       </c>
       <c r="B233" s="17" t="inlineStr">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -12638,7 +12638,7 @@
       </c>
       <c r="E231" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F231" s="13" t="n"/>
@@ -12652,7 +12652,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I231" s="15" t="inlineStr"/>
+      <c r="I231" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-09 (PR #117): a1111.ts passes the unmodified shared conformance suite twice, for a default server and for one started with --api-auth, against mocked HTTP built from the A1111 API source (force_task_id, /internal/progress, /sdapi/v1/interrupt, the --nowebui fallback, HTTP Basic). a1111.test.ts: 58 passed. Live check against a running A1111 / Forge server still pending.</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
@@ -12677,7 +12681,7 @@
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F232" s="13" t="n"/>
@@ -12691,7 +12695,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I232" s="15" t="inlineStr"/>
+      <c r="I232" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-09 (PR #117): replicate.ts, falAi.ts and stabilityAi.ts each pass the unmodified shared conformance suite against mocked HTTP fixtures taken from the providers' official API documents (async polling for Replicate and fal.ai, errors, rate limits, cancellation, timeouts). replicate.test.ts 39, falAi.test.ts 42, stabilityAi.test.ts 39 passed. Keys are read from the OS credential store (media_secret_* commands, keyring) and never stored in the descriptor. Live-provider checks pending: no API keys were available.</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
